--- a/consent_forms/041_field_visit_documentation_consent--consent_forms.xlsx
+++ b/consent_forms/041_field_visit_documentation_consent--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'yes',_'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Yes', 'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'no',_'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'No', 'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'photos_1',_'label':_'photos_1'}</t>
+          <t>photos_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'photos_1', 'label': 'Photos 1'}</t>
+          <t>Photos 1</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'photos_2',_'label':_'photos_2'}</t>
+          <t>photos_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'photos_2', 'label': 'Photos 2'}</t>
+          <t>Photos 2</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'video_1',_'label':_'video_1'}</t>
+          <t>video_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'video_1', 'label': 'Video 1'}</t>
+          <t>Video 1</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'video_2',_'label':_'video_2'}</t>
+          <t>video_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'video_2', 'label': 'Video 2'}</t>
+          <t>Video 2</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'yes',_'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Yes', 'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'no',_'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'No', 'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
